--- a/Team-Data/2014-15/3-20-2014-15.xlsx
+++ b/Team-Data/2014-15/3-20-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" t="n">
         <v>53</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>0.768</v>
+        <v>0.779</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -685,13 +752,13 @@
         <v>0.465</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="M2" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.384</v>
+        <v>0.383</v>
       </c>
       <c r="O2" t="n">
         <v>17.1</v>
@@ -709,19 +776,19 @@
         <v>32</v>
       </c>
       <c r="T2" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U2" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="V2" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W2" t="n">
         <v>8.9</v>
       </c>
       <c r="X2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y2" t="n">
         <v>4.9</v>
@@ -733,13 +800,13 @@
         <v>20.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.7</v>
+        <v>102.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -754,10 +821,10 @@
         <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
         <v>4</v>
@@ -775,16 +842,16 @@
         <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -793,13 +860,13 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
         <v>17</v>
@@ -808,13 +875,13 @@
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB2" t="n">
         <v>10</v>
       </c>
       <c r="BC2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E3" t="n">
         <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>0.441</v>
+        <v>0.448</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
@@ -864,16 +931,16 @@
         <v>88.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L3" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
       <c r="O3" t="n">
         <v>15</v>
@@ -882,7 +949,7 @@
         <v>20</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.748</v>
+        <v>0.749</v>
       </c>
       <c r="R3" t="n">
         <v>11.2</v>
@@ -891,10 +958,10 @@
         <v>32.6</v>
       </c>
       <c r="T3" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U3" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="V3" t="n">
         <v>14</v>
@@ -903,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y3" t="n">
         <v>5.3</v>
@@ -912,22 +979,22 @@
         <v>21.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.8</v>
+        <v>101</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>19</v>
       </c>
       <c r="AF3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG3" t="n">
         <v>19</v>
@@ -951,13 +1018,13 @@
         <v>12</v>
       </c>
       <c r="AN3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
       </c>
       <c r="AP3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
         <v>18</v>
@@ -969,31 +1036,31 @@
         <v>12</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -1025,85 +1092,85 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" t="n">
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>0.418</v>
+        <v>0.409</v>
       </c>
       <c r="H4" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J4" t="n">
-        <v>82.5</v>
+        <v>82.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.326</v>
+        <v>0.324</v>
       </c>
       <c r="O4" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="P4" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.742</v>
+        <v>0.741</v>
       </c>
       <c r="R4" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S4" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T4" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U4" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="AB4" t="n">
-        <v>97</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.5</v>
+        <v>-3.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1115,16 +1182,16 @@
         <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1139,10 +1206,10 @@
         <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR4" t="n">
         <v>22</v>
@@ -1154,10 +1221,10 @@
         <v>22</v>
       </c>
       <c r="AU4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1166,19 +1233,19 @@
         <v>25</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB4" t="n">
         <v>23</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" t="n">
         <v>29</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>0.433</v>
+        <v>0.439</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
@@ -1225,7 +1292,7 @@
         <v>35.8</v>
       </c>
       <c r="J5" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="K5" t="n">
         <v>0.424</v>
@@ -1234,31 +1301,31 @@
         <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N5" t="n">
         <v>0.314</v>
       </c>
       <c r="O5" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P5" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0.745</v>
       </c>
       <c r="R5" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="T5" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U5" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V5" t="n">
         <v>12</v>
@@ -1276,28 +1343,28 @@
         <v>18.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB5" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.4</v>
+        <v>-2.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
@@ -1336,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,10 +1415,10 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -1389,46 +1456,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
         <v>28</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6</v>
+        <v>0.594</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J6" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L6" t="n">
         <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="N6" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O6" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P6" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R6" t="n">
         <v>11.9</v>
@@ -1440,46 +1507,46 @@
         <v>45.9</v>
       </c>
       <c r="U6" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="V6" t="n">
         <v>14.1</v>
       </c>
       <c r="W6" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X6" t="n">
         <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z6" t="n">
         <v>18.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.9</v>
+        <v>100.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="n">
         <v>23</v>
@@ -1518,7 +1585,7 @@
         <v>3</v>
       </c>
       <c r="AU6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV6" t="n">
         <v>14</v>
@@ -1527,19 +1594,19 @@
         <v>29</v>
       </c>
       <c r="AX6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA6" t="n">
         <v>4</v>
       </c>
-      <c r="AY6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5</v>
-      </c>
       <c r="BB6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
         <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>0.634</v>
+        <v>0.629</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
@@ -1592,7 +1659,7 @@
         <v>82.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L7" t="n">
         <v>9.800000000000001</v>
@@ -1607,7 +1674,7 @@
         <v>18.4</v>
       </c>
       <c r="P7" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0.757</v>
@@ -1619,16 +1686,16 @@
         <v>31.7</v>
       </c>
       <c r="T7" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V7" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X7" t="n">
         <v>4.1</v>
@@ -1643,16 +1710,16 @@
         <v>20.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>103.5</v>
+        <v>103.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1661,16 +1728,16 @@
         <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>14</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1679,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
@@ -1688,7 +1755,7 @@
         <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
@@ -1700,13 +1767,13 @@
         <v>19</v>
       </c>
       <c r="AU7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV7" t="n">
         <v>12</v>
       </c>
-      <c r="AV7" t="n">
-        <v>11</v>
-      </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -1768,13 +1835,13 @@
         <v>48.4</v>
       </c>
       <c r="I8" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="J8" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L8" t="n">
         <v>9.300000000000001</v>
@@ -1783,34 +1850,34 @@
         <v>26.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O8" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P8" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="R8" t="n">
         <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
         <v>22.6</v>
       </c>
       <c r="V8" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X8" t="n">
         <v>4.7</v>
@@ -1819,31 +1886,31 @@
         <v>3.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="AB8" t="n">
         <v>104.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="n">
         <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1861,34 +1928,34 @@
         <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
         <v>19</v>
       </c>
       <c r="AS8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT8" t="n">
         <v>23</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>24</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX8" t="n">
         <v>16</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" t="n">
         <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>0.371</v>
+        <v>0.377</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1953,37 +2020,37 @@
         <v>37.4</v>
       </c>
       <c r="J9" t="n">
-        <v>86.7</v>
+        <v>86.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L9" t="n">
         <v>7.8</v>
       </c>
       <c r="M9" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.319</v>
+        <v>0.32</v>
       </c>
       <c r="O9" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P9" t="n">
         <v>24.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.729</v>
+        <v>0.731</v>
       </c>
       <c r="R9" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S9" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T9" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="U9" t="n">
         <v>21.6</v>
@@ -1992,28 +2059,28 @@
         <v>14.1</v>
       </c>
       <c r="W9" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X9" t="n">
         <v>4.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>100.2</v>
+        <v>100.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2025,13 +2092,13 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK9" t="n">
         <v>26</v>
@@ -2058,37 +2125,37 @@
         <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
         <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB9" t="n">
         <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-2</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG10" t="n">
         <v>24</v>
@@ -2228,7 +2295,7 @@
         <v>22</v>
       </c>
       <c r="AO10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP10" t="n">
         <v>16</v>
@@ -2255,7 +2322,7 @@
         <v>16</v>
       </c>
       <c r="AX10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
@@ -2267,7 +2334,7 @@
         <v>22</v>
       </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2366,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="J11" t="n">
         <v>86.8</v>
@@ -2323,28 +2390,28 @@
         <v>0.478</v>
       </c>
       <c r="L11" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="M11" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
       <c r="O11" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R11" t="n">
         <v>10.2</v>
       </c>
       <c r="S11" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="T11" t="n">
         <v>44.5</v>
@@ -2353,7 +2420,7 @@
         <v>27.3</v>
       </c>
       <c r="V11" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W11" t="n">
         <v>9.5</v>
@@ -2371,13 +2438,13 @@
         <v>18.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>109.8</v>
+        <v>109.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2395,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
@@ -2410,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
@@ -2419,7 +2486,7 @@
         <v>8</v>
       </c>
       <c r="AR11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
         <v>4</v>
@@ -2434,7 +2501,7 @@
         <v>19</v>
       </c>
       <c r="AW11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX11" t="n">
         <v>1</v>
@@ -2443,7 +2510,7 @@
         <v>2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA11" t="n">
         <v>27</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.672</v>
+        <v>0.676</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>84.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
@@ -2511,25 +2578,25 @@
         <v>33.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="P12" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="R12" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S12" t="n">
         <v>31.8</v>
       </c>
       <c r="T12" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U12" t="n">
         <v>22.1</v>
@@ -2541,25 +2608,25 @@
         <v>9.5</v>
       </c>
       <c r="X12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y12" t="n">
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2571,13 +2638,13 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2589,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
@@ -2607,31 +2674,31 @@
         <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E13" t="n">
         <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G13" t="n">
-        <v>0.441</v>
+        <v>0.448</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2696,13 +2763,13 @@
         <v>0.338</v>
       </c>
       <c r="O13" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P13" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="R13" t="n">
         <v>10.3</v>
@@ -2717,7 +2784,7 @@
         <v>21.4</v>
       </c>
       <c r="V13" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W13" t="n">
         <v>6.2</v>
@@ -2735,25 +2802,25 @@
         <v>21.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>96.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="n">
         <v>19</v>
       </c>
       <c r="AF13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG13" t="n">
         <v>19</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
@@ -2771,19 +2838,19 @@
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP13" t="n">
         <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
@@ -2792,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="AU13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -2845,58 +2912,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" t="n">
         <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>0.643</v>
+        <v>0.638</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="J14" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L14" t="n">
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.375</v>
+        <v>0.373</v>
       </c>
       <c r="O14" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P14" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.712</v>
+        <v>0.713</v>
       </c>
       <c r="R14" t="n">
         <v>9.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T14" t="n">
         <v>42.2</v>
       </c>
       <c r="U14" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="V14" t="n">
         <v>12.3</v>
@@ -2908,25 +2975,25 @@
         <v>4.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Z14" t="n">
         <v>21.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.1</v>
+        <v>106</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2938,7 +3005,7 @@
         <v>29</v>
       </c>
       <c r="AI14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ14" t="n">
         <v>15</v>
@@ -2983,7 +3050,7 @@
         <v>14</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -2998,7 +3065,7 @@
         <v>2</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -3027,55 +3094,55 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>0.258</v>
+        <v>0.254</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N15" t="n">
         <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.741</v>
+        <v>0.743</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="T15" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="U15" t="n">
         <v>20.9</v>
@@ -3090,22 +3157,22 @@
         <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.9</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,16 +3184,16 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
         <v>25</v>
@@ -3135,22 +3202,22 @@
         <v>24</v>
       </c>
       <c r="AN15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
         <v>12</v>
       </c>
       <c r="AP15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS15" t="n">
         <v>13</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>11</v>
       </c>
       <c r="AT15" t="n">
         <v>9</v>
@@ -3162,7 +3229,7 @@
         <v>5</v>
       </c>
       <c r="AW15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX15" t="n">
         <v>21</v>
@@ -3171,13 +3238,13 @@
         <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
         <v>23</v>
       </c>
       <c r="BB15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F16" t="n">
         <v>21</v>
       </c>
       <c r="G16" t="n">
-        <v>0.696</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
@@ -3227,67 +3294,67 @@
         <v>37.8</v>
       </c>
       <c r="J16" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L16" t="n">
         <v>5.1</v>
       </c>
       <c r="M16" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.339</v>
+        <v>0.337</v>
       </c>
       <c r="O16" t="n">
         <v>18.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.777</v>
+        <v>0.778</v>
       </c>
       <c r="R16" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S16" t="n">
         <v>32.3</v>
       </c>
       <c r="T16" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U16" t="n">
         <v>21.8</v>
       </c>
       <c r="V16" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y16" t="n">
         <v>5.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>99</v>
+        <v>98.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3299,16 +3366,16 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ16" t="n">
         <v>20</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,19 +3384,19 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>7</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AR16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS16" t="n">
         <v>14</v>
@@ -3338,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV16" t="n">
         <v>6</v>
@@ -3347,7 +3414,7 @@
         <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY16" t="n">
         <v>22</v>
@@ -3356,7 +3423,7 @@
         <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
         <v>17</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -3391,43 +3458,43 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17" t="n">
         <v>36</v>
       </c>
       <c r="G17" t="n">
-        <v>0.471</v>
+        <v>0.463</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
       </c>
       <c r="I17" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="J17" t="n">
         <v>76.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L17" t="n">
         <v>6.9</v>
       </c>
       <c r="M17" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O17" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P17" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Q17" t="n">
         <v>0.743</v>
@@ -3436,22 +3503,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T17" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="U17" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W17" t="n">
         <v>8.1</v>
       </c>
       <c r="X17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y17" t="n">
         <v>4.2</v>
@@ -3463,13 +3530,13 @@
         <v>20.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3502,13 +3569,13 @@
         <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
         <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3529,7 +3596,7 @@
         <v>10</v>
       </c>
       <c r="AX17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY17" t="n">
         <v>6</v>
@@ -3544,7 +3611,7 @@
         <v>26</v>
       </c>
       <c r="BC17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" t="n">
         <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
-        <v>0.493</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J18" t="n">
-        <v>81.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.456</v>
+        <v>0.458</v>
       </c>
       <c r="L18" t="n">
         <v>6.8</v>
@@ -3603,31 +3670,31 @@
         <v>18.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="O18" t="n">
         <v>16.2</v>
       </c>
       <c r="P18" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R18" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="S18" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T18" t="n">
-        <v>42.2</v>
+        <v>41.6</v>
       </c>
       <c r="U18" t="n">
         <v>23.2</v>
       </c>
       <c r="V18" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="W18" t="n">
         <v>9.4</v>
@@ -3639,19 +3706,19 @@
         <v>4.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3663,16 +3730,16 @@
         <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AI18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL18" t="n">
         <v>23</v>
@@ -3690,16 +3757,16 @@
         <v>25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AS18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -3711,22 +3778,22 @@
         <v>4</v>
       </c>
       <c r="AX18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY18" t="n">
         <v>14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
         <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-8</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3851,10 +3918,10 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3872,7 +3939,7 @@
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3881,16 +3948,16 @@
         <v>30</v>
       </c>
       <c r="AT19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX19" t="n">
         <v>27</v>
@@ -3902,10 +3969,10 @@
         <v>10</v>
       </c>
       <c r="BA19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -3940,64 +4007,64 @@
         <v>68</v>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>0.529</v>
+        <v>0.544</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>82.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.363</v>
+        <v>0.359</v>
       </c>
       <c r="O20" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.761</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T20" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="U20" t="n">
         <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="W20" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X20" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="Y20" t="n">
         <v>5.9</v>
@@ -4006,16 +4073,16 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
@@ -4030,7 +4097,7 @@
         <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
         <v>18</v>
@@ -4039,34 +4106,34 @@
         <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM20" t="n">
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS20" t="n">
         <v>17</v>
       </c>
       <c r="AT20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AU20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -4119,46 +4186,46 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" t="n">
         <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G21" t="n">
-        <v>0.203</v>
+        <v>0.206</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>35.4</v>
+        <v>35.6</v>
       </c>
       <c r="J21" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.429</v>
+        <v>0.43</v>
       </c>
       <c r="L21" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M21" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O21" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="P21" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.765</v>
+        <v>0.763</v>
       </c>
       <c r="R21" t="n">
         <v>10.8</v>
@@ -4170,7 +4237,7 @@
         <v>40.6</v>
       </c>
       <c r="U21" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V21" t="n">
         <v>14.3</v>
@@ -4179,25 +4246,25 @@
         <v>7.1</v>
       </c>
       <c r="X21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y21" t="n">
         <v>4.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA21" t="n">
         <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>92.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-8.9</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4209,13 +4276,13 @@
         <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI21" t="n">
         <v>27</v>
       </c>
       <c r="AJ21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK21" t="n">
         <v>27</v>
@@ -4227,7 +4294,7 @@
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
         <v>29</v>
@@ -4248,16 +4315,16 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
         <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY21" t="n">
         <v>8</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E22" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F22" t="n">
         <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4322,25 +4389,25 @@
         <v>86.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L22" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M22" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="O22" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P22" t="n">
         <v>24.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.769</v>
+        <v>0.766</v>
       </c>
       <c r="R22" t="n">
         <v>12.6</v>
@@ -4349,16 +4416,16 @@
         <v>35.1</v>
       </c>
       <c r="T22" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="U22" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V22" t="n">
         <v>14.9</v>
       </c>
       <c r="W22" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X22" t="n">
         <v>5.9</v>
@@ -4373,13 +4440,13 @@
         <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.4</v>
+        <v>103.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4394,7 +4461,7 @@
         <v>13</v>
       </c>
       <c r="AI22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
         <v>4</v>
@@ -4409,7 +4476,7 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4418,7 +4485,7 @@
         <v>7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4433,7 +4500,7 @@
         <v>22</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
         <v>22</v>
@@ -4442,16 +4509,16 @@
         <v>6</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
         <v>29</v>
       </c>
       <c r="BA22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC22" t="n">
         <v>11</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -4486,28 +4553,28 @@
         <v>70</v>
       </c>
       <c r="E23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314</v>
+        <v>0.3</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J23" t="n">
-        <v>82.5</v>
+        <v>82.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
         <v>19.6</v>
@@ -4516,52 +4583,52 @@
         <v>0.354</v>
       </c>
       <c r="O23" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="P23" t="n">
         <v>19.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.726</v>
+        <v>0.725</v>
       </c>
       <c r="R23" t="n">
         <v>9.6</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
         <v>41.2</v>
       </c>
       <c r="U23" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W23" t="n">
         <v>7.9</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA23" t="n">
         <v>18.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.2</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.6</v>
+        <v>-6</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4576,22 +4643,22 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ23" t="n">
         <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4606,25 +4673,25 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
       </c>
       <c r="AU23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>18</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -4665,25 +4732,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F24" t="n">
         <v>52</v>
       </c>
       <c r="G24" t="n">
-        <v>0.246</v>
+        <v>0.235</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="J24" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K24" t="n">
         <v>0.409</v>
@@ -4692,34 +4759,34 @@
         <v>8.1</v>
       </c>
       <c r="M24" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.318</v>
+        <v>0.317</v>
       </c>
       <c r="O24" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P24" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.674</v>
+        <v>0.673</v>
       </c>
       <c r="R24" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S24" t="n">
         <v>31.3</v>
       </c>
       <c r="T24" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U24" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V24" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="W24" t="n">
         <v>9.800000000000001</v>
@@ -4737,16 +4804,16 @@
         <v>20.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>91.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="AC24" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF24" t="n">
         <v>28</v>
@@ -4755,13 +4822,13 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
@@ -4785,7 +4852,7 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4794,7 +4861,7 @@
         <v>18</v>
       </c>
       <c r="AU24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,16 +4870,16 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>0.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -4937,16 +5004,16 @@
         <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ25" t="n">
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL25" t="n">
         <v>8</v>
@@ -4961,22 +5028,22 @@
         <v>17</v>
       </c>
       <c r="AP25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR25" t="n">
         <v>13</v>
       </c>
       <c r="AS25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV25" t="n">
         <v>25</v>
@@ -5000,7 +5067,7 @@
         <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E26" t="n">
         <v>44</v>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G26" t="n">
-        <v>0.657</v>
+        <v>0.667</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
@@ -5047,28 +5114,28 @@
         <v>38.4</v>
       </c>
       <c r="J26" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L26" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="M26" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P26" t="n">
         <v>20</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.799</v>
+        <v>0.797</v>
       </c>
       <c r="R26" t="n">
         <v>10.8</v>
@@ -5080,7 +5147,7 @@
         <v>46</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="V26" t="n">
         <v>13.8</v>
@@ -5092,7 +5159,7 @@
         <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
         <v>18.4</v>
@@ -5104,25 +5171,25 @@
         <v>102.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG26" t="n">
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ26" t="n">
         <v>8</v>
@@ -5143,13 +5210,13 @@
         <v>26</v>
       </c>
       <c r="AP26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5158,7 +5225,7 @@
         <v>2</v>
       </c>
       <c r="AU26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV26" t="n">
         <v>9</v>
@@ -5167,7 +5234,7 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F27" t="n">
         <v>45</v>
       </c>
       <c r="G27" t="n">
-        <v>0.338</v>
+        <v>0.328</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
@@ -5235,28 +5302,28 @@
         <v>0.451</v>
       </c>
       <c r="L27" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M27" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="O27" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="P27" t="n">
         <v>29.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.777</v>
+        <v>0.778</v>
       </c>
       <c r="R27" t="n">
         <v>11.1</v>
       </c>
       <c r="S27" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="T27" t="n">
         <v>44.6</v>
@@ -5265,31 +5332,31 @@
         <v>19.9</v>
       </c>
       <c r="V27" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="W27" t="n">
         <v>6.5</v>
       </c>
       <c r="X27" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z27" t="n">
         <v>21</v>
       </c>
       <c r="AA27" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AB27" t="n">
         <v>101</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.3</v>
+        <v>-4.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,10 +5368,10 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5334,10 +5401,10 @@
         <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5352,7 +5419,7 @@
         <v>28</v>
       </c>
       <c r="AY27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ27" t="n">
         <v>17</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -5411,46 +5478,46 @@
         <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.361</v>
+        <v>0.366</v>
       </c>
       <c r="O28" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P28" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U28" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="V28" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="W28" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X28" t="n">
         <v>5.5</v>
@@ -5459,7 +5526,7 @@
         <v>4.7</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA28" t="n">
         <v>20.1</v>
@@ -5468,10 +5535,10 @@
         <v>102.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
         <v>9</v>
@@ -5486,13 +5553,13 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ28" t="n">
         <v>14</v>
       </c>
       <c r="AK28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,7 +5568,7 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
@@ -5516,7 +5583,7 @@
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>16</v>
@@ -5528,7 +5595,7 @@
         <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
@@ -5540,7 +5607,7 @@
         <v>11</v>
       </c>
       <c r="BA28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB28" t="n">
         <v>11</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E29" t="n">
         <v>41</v>
       </c>
       <c r="F29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>0.594</v>
+        <v>0.603</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J29" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="K29" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L29" t="n">
         <v>8.9</v>
@@ -5605,7 +5672,7 @@
         <v>25.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O29" t="n">
         <v>19.5</v>
@@ -5614,28 +5681,28 @@
         <v>24.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R29" t="n">
         <v>10.8</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T29" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U29" t="n">
         <v>20.8</v>
       </c>
       <c r="V29" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W29" t="n">
         <v>7.7</v>
       </c>
       <c r="X29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y29" t="n">
         <v>5.2</v>
@@ -5647,22 +5714,22 @@
         <v>20.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>104.3</v>
+        <v>104.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF29" t="n">
         <v>10</v>
       </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH29" t="n">
         <v>13</v>
@@ -5689,7 +5756,7 @@
         <v>4</v>
       </c>
       <c r="AP29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
         <v>3</v>
@@ -5707,7 +5774,7 @@
         <v>21</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW29" t="n">
         <v>15</v>
@@ -5716,13 +5783,13 @@
         <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ29" t="n">
         <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AE30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF30" t="n">
         <v>18</v>
@@ -5856,7 +5923,7 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="n">
         <v>17</v>
@@ -5865,7 +5932,7 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO30" t="n">
         <v>16</v>
@@ -5895,7 +5962,7 @@
         <v>21</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY30" t="n">
         <v>12</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E31" t="n">
         <v>40</v>
       </c>
       <c r="F31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.58</v>
+        <v>0.588</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
@@ -5957,10 +6024,10 @@
         <v>38.4</v>
       </c>
       <c r="J31" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.467</v>
+        <v>0.468</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
@@ -5969,7 +6036,7 @@
         <v>16.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O31" t="n">
         <v>15.8</v>
@@ -5978,7 +6045,7 @@
         <v>21.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="R31" t="n">
         <v>10.4</v>
@@ -5987,10 +6054,10 @@
         <v>33.6</v>
       </c>
       <c r="T31" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U31" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="V31" t="n">
         <v>15</v>
@@ -6005,25 +6072,25 @@
         <v>4.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA31" t="n">
         <v>19.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
       </c>
       <c r="AF31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG31" t="n">
         <v>12</v>
@@ -6032,7 +6099,7 @@
         <v>13</v>
       </c>
       <c r="AI31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ31" t="n">
         <v>24</v>
@@ -6056,13 +6123,13 @@
         <v>24</v>
       </c>
       <c r="AQ31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR31" t="n">
         <v>20</v>
       </c>
-      <c r="AR31" t="n">
-        <v>21</v>
-      </c>
       <c r="AS31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
         <v>11</v>
@@ -6071,7 +6138,7 @@
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW31" t="n">
         <v>20</v>
@@ -6083,13 +6150,13 @@
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
         <v>21</v>
       </c>
       <c r="BB31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-20-2014-15</t>
+          <t>2015-03-20</t>
         </is>
       </c>
     </row>
